--- a/Cumulative_Outputs/Results/Results_T-All_K1.N10.P100.xlsx
+++ b/Cumulative_Outputs/Results/Results_T-All_K1.N10.P100.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Boolean_Network_SISOR_Degeneracy_Simulator\Boolean_Network_SISOR_Degeneracy_Simulator\Cumulative_Outputs\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38102677-3271-4D07-A613-EE1E0E74987B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4EEA9DA-9E41-488A-9DFE-8658218408A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" activeTab="2" xr2:uid="{8979E4B9-F6D3-4FFF-BFAD-32F04701C466}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
   <si>
     <t>Identifier</t>
   </si>
@@ -130,6 +130,12 @@
   </si>
   <si>
     <t>0a8c5c9f3b8b0d711510c46c19219bab89c89cebb6d7397aa3a8a7ccec1265e8</t>
+  </si>
+  <si>
+    <t>Average per ID</t>
+  </si>
+  <si>
+    <t>Average per Timestep</t>
   </si>
 </sst>
 </file>
@@ -1383,7 +1389,7 @@
         <v>19</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>21</v>
@@ -1898,7 +1904,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B18" s="5">
         <f>AVERAGE(B2:B3)</f>

--- a/Cumulative_Outputs/Results/Results_T-All_K1.N10.P100.xlsx
+++ b/Cumulative_Outputs/Results/Results_T-All_K1.N10.P100.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Boolean_Network_SISOR_Degeneracy_Simulator\Boolean_Network_SISOR_Degeneracy_Simulator\Cumulative_Outputs\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4EEA9DA-9E41-488A-9DFE-8658218408A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE645523-82EE-456F-B76F-79CE1ED44DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" activeTab="2" xr2:uid="{8979E4B9-F6D3-4FFF-BFAD-32F04701C466}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{8979E4B9-F6D3-4FFF-BFAD-32F04701C466}"/>
   </bookViews>
   <sheets>
     <sheet name="T-All_K1 N10 P100" sheetId="8" r:id="rId1"/>
